--- a/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
+++ b/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11508" windowHeight="6264" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="barcode" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>槽號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,33 +79,23 @@
     <t>https://qr.calm9.com/tw/</t>
   </si>
   <si>
+    <t>批號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>供應商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>送達地點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>E1550156A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E309</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25531E3091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>批號</t>
+    <t>5E319</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -122,19 +112,11 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>25531E3091</t>
+      <t>26206E3191</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>供應商</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>送達地點</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>項次</t>
   </si>
   <si>
@@ -150,16 +132,29 @@
     <t>E29</t>
   </si>
   <si>
+    <t>26814E29J1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>15P5</t>
   </si>
   <si>
     <t>E44</t>
   </si>
   <si>
+    <t>26814E44J1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>E318</t>
   </si>
   <si>
+    <t>26814E3181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>15P6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>E319</t>
@@ -168,12 +163,19 @@
     <t>26813E3191</t>
   </si>
   <si>
+    <t>15P6</t>
+  </si>
+  <si>
     <t>E315</t>
   </si>
   <si>
     <t>26813E3151</t>
   </si>
   <si>
+    <t>15P5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>E320</t>
   </si>
   <si>
@@ -181,33 +183,13 @@
   </si>
   <si>
     <t>18P1</t>
-  </si>
-  <si>
-    <t>26814E29J1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26814E3181</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15P6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15P5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26814E44J1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,20 +228,6 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Free 3 of 9 Extended"/>
     </font>
     <font>
       <sz val="12"/>
@@ -323,17 +291,24 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="36"/>
-      <color theme="1"/>
-      <name val="IDAutomationSC128L DEMO"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF262626"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -344,27 +319,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -438,91 +398,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -552,8 +521,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>290882</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2696625</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -584,79 +553,28 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>263071</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>72571</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2180544</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>879928</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>307571</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>307571</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="圖片 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2812142" y="9125857"/>
-          <a:ext cx="1917473" cy="807357"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>117928</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>84364</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>29935</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="圖片 12" descr="http://s05.calm9.com/qrcode/2025-06/MNBYJV7GEQ.png"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAHsAAAB7CAYAAABUx/9/AAAAAXNSR0IArs4c6QAAAARnQU1BAACxjwv8YQUAAAAJcEhZcwAADsMAAA7DAcdvqGQAAAuCSURBVHhe7Y/RkhzJEcP8/z8td92NtZhaopfp6tGTEIFQNMmsWf3n4tfTEssbeGs2pLvlCfaO5WS6edAYHkksb+Ct2ZDulifYO5aT6eZBY3gksbyBt2ZDulueYO9YTqabB/36OMHemeZPwfdNo9kQ21tObGP5FL5z+fyjZJo/Bd83jWZDbG85sY3lU/jO5fOPkmn+FHzfNJoNsb3lxDaWT+E7l/lR5iZpckpSfypp8kaS+qXRbIjtmZtk66pRlDQ5Jak/lTR5I0n90mg2xPbMTbJ11ShKmpyS1J9KmryRpH5pNBtie+Ym2bpqFCWWN5zcEr7TaDQbwj010nZJmtwkW1eNosTyhpNbwncajWZDuKdG2i5Jk5tk66pRlFjecHJL+E6j0WwI99RI2yVpcpNsXTWKEssN7hsN2zCnDeluSSw3uKeGbZibZOuqUZRYbnDfaNiGOW1Id0tiucE9NWzD3CRbV42ixHKD+0bDNsxpQ7pbEssN7qlhG+Ym2bo8mmLvMG9sSHfLhmZvmyZvbJjuDb5z+fyjhHljQ7pbNjR72zR5Y8N0b/Cdy+cfJcwbG9LdsqHZ26bJGxume4PvXL59PCL5m//LSf6gMTyS/M3/5SR/0BgeSf7m/3KSP+br7Y8Rf/SywfaWE9swp8Z0Q41m8wk+/mv8j9EG21tObMOcGtMNNZrNJ/j4r/E/RhtsbzmxDXNqTDfUaDafQH+Nf5BJmpxOmd7avsmpkbatJPV3Gmn7zdf2G3G8SZqcTpne2r7JqZG2rST1dxpp+83X9htxvEmanE6Z3tq+yamRtq0k9XcaaRv8+iBNThvS3W6D7Zmbhm2eysnJhnkjub61+DGnDelut8H2zE3DNk/l5GTDvJFc31r8mNOGdLfbYHvmpmGbp3JysmHeSN6+bNTw1K1pTDeNJPVLYnnD9Ha6J28XRw89dGsa000jSf2SWN4wvZ3uydvF0UMP3ZrGdNNIUr8kljdMb6d7Ul1Mf8D2zKlhmyanDelu2ZDulg3N3jbj/PXvLXZs2J45NWzT5LQh3S0b0t2yodnbZpy//r3Fjg3bM6eGbZqcNqS7ZUO6WzY0e9v8H3kuCDeUpH5JLCfcUCNt7zSmG2qk7ZKkfkmanJKtyyPCDSWpXxLLCTfUSNs7jemGGmm7JKlfkianZOvyiHBDSeqXxHLCDTXS9k5juqFG2i5J6pekySnZumr0W2K5YXvmU420XZLUL0nqlyT1S2O6aTS2XT5gTonlhu2ZTzXSdklSvySpX5LUL43pptHYdvmAOSWWG7ZnPtVI2yVJ/ZKkfklSvzSmm0bjbffK/oGFYRvLyXRDjbTdNdK2taHZc0ONtF0SzV///oONiG0sJ9MNNdJ210jb1oZmzw010nZJNH/9+w82IraxnEw31EjbXSNtWxuaPTfUSNslucnfj/4nmeak2Ri8NY20XRq2sdz49P6E6ze+foySaU6ajcFb00jbpWEby41P70+4fuPrxyiZ5qTZGLw1jbRdGrax3Pj0/gT9Bf4RJrHc4N400naXpL6VpH5JUr9LUr8kTW6S9y+QDneJ5Qb3ppG2uyT1rST1S5L6XZL6JWlyk7x/gXS4Syw3uDeNtN0lqW8lqV+S1O+S1C9Jk5vk+s4jOsVum7zRSNulkbZLo9k0NO/Ypskpub7ziE6x2yZvNNJ2aaTt0mg2Dc07tmlySq7vPKJT7LbJG420XRppuzSaTUPzjm2anJLqr7Zjwg0llpPphpJpfkLzpm2eyhuqi+YHuKHEcjLdUDLNT2jetM1TeUN10fwAN5RYTqYbSqb5Cc2btnkqb7huZo8ypyT1S5L63SnTW+5NMs0beEuJ5VOu+9kPMKck9UuS+t0p01vuTTLNG3hLieVTrvvZDzCnJPVLkvrdKdNb7k0yzRt4S4nlU6779x9Jkqdywg0lqd8lqV+S1C8bntpbTmzDnBpXlw8oeSon3FCS+l2S+iVJ/bLhqb3lxDbMqXF1+YCSp3LCDSWp3yWpX5LULxue2ltObMOcGleXR8zpCem9U6ekN3YN2zCnJPVLwzbMqbHt8gFzekJ679Qp6Y1dwzbMKUn90rANc2psu3zAnJ6Q3jt1Snpj17ANc0pSvzRsw5wab7tX9g2ODG5McpI/JUn9rpG2u8RyYhvmZoOumoe4MclJ/pQk9btG2u4Sy4ltmJsNumoe4sYkJ/lTktTvGmm7SywntmFuNly7nw+aTYO9w/xEkvo7SZObDeluSVK/a6Tty68Po9k02DvMTySpv5M0udmQ7pYk9btG2r78+jCaTYO9w/xEkvo7SZObDeluSVK/a6Ttyxi+2ZDudknqd0nqd4203W2wPfNGkvolaXJqXF0+oA3pbpekfpekftdI290G2zNvJKlfkianxtXlA9qQ7nZJ6ndJ6neNtN1tsD3zRpL6JWlyamhTHcuGuUmanJLUL4nlU/gOJZaT6WYqeete2Tc4MmzD3CRNTknql8TyKXyHEsvJdDOVvHWv7BscGbZhbpImpyT1S2L5FL5DieVkuplK3rpXVvN2LJImN420PZWkfpekftdI26XRbIzxBX/MJE1uGml7Kkn9Lkn9rpG2S6PZGOML/phJmtw00vZUkvpdkvpdI22XRrMx3i7soZOcNqS7ZUO6u5NYbnBPjbRdkmlu2P7tS0cHOW1Id8uGdHcnsdzgnhppuyTT3LD925eODnLakO6WDenuTmK5wT010nZJprlh++tbiz+mYRvmjST1uw3prpWkfkmanJKtq0Yf1bAN80aS+t2GdNdKUr8kTU7J1lWjj2rYhnkjSf1uQ7prJalfkianZOuq0W+npDd2SeqXJ6T3dknqlyT1y4ZmbxvLDe4v8zFzOiW9sUtSvzwhvbdLUr8kqV82NHvbWG5wf5mPmdMp6Y1dkvrlCem9XZL6JUn9sqHZ28Zyg/vLfMz8RKPZEO4bSeqXhm2anJImpyT1reT61uIRjWZDuG8kqV8atmlySpqcktS3kutbi0c0mg3hvpGkfmnYpskpaXJKUt9Kru9cGNxTkvolSf2ywfbM6ZTpbbOfbiix3OD+8uj4tyT1S5L6ZYPtmdMp09tmP91QYrnB/eXR8W9J6pck9csG2zOnU6a3zX66ocRyg/vLfMzcJKlfNtieuWmk7W5DujuVpP5JyfWtxY+S1C8bbM/cNNJ2tyHdnUpS/6Tk+tbiR0nqlw22Z24aabvbkO5OJal/UtL9jw9If8BuQ7pbEsuJbSwnzYbYnjltONl3Fwe8/ZjYkO6WxHJiG8tJsyG2Z04bTvbdxQFvPyY2pLslsZzYxnLSbIjtmdOGk/3l28cjNqS75Qmffoe5SZqckian5CZ/P3rChnS3POHT7zA3SZNT0uSU3OTvR0/YkO6WJ3z6HeYmaXJKmpySmzwXU07emd5y33iCvdPkJrHc4J6SmzwXU07emd5y33iCvdPkJrHc4J6SmzwXU07emd5y33iCvdPkJrHc4J6Sm/znA5M0OTVsYznhhpLULxvS3Z0N6e5UsnXVKEqanBq2sZxwQ0nqlw3p7s6GdHcq2bpqFCVNTg3bWE64oST1y4Z0d2dDujuVbF01ipImp4ZtLG+Y3nJvTklv7Dac7C/zMXOTNDk1bGN5w/SWe3NKemO34WR/mY+Zm6TJqWEbyxumt9ybU9Ibuw0n+8t8zNwkJzkl09zg3iSp3yV/MjfJTf7zgUlOckqmucG9SVK/S/5kbpKb/OcDk5zklExzg3uTpH6X/MncJDd5LqZM3znZU3KSUyNtd4203SXTnNjm+v75uGH6zsmekpOcGmm7a6TtLpnmxDbX98/HDdN3TvaUnOTUSNtdI213yTQntrm+v4qnNNJ2l1hObMOcGrZp8qmGbZg3GleXD0400naXWE5sw5watmnyqYZtmDcaV5cPTjTSdpdYTmzDnBq2afKphm2YN2Z+/fovg4vjE2rXioQAAAAASUVORK5CYII="/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5361214" y="1424214"/>
-          <a:ext cx="1172936" cy="1174750"/>
+          <a:off x="14223076" y="6192982"/>
+          <a:ext cx="307571" cy="307571"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -672,39 +590,125 @@
           </a:ext>
         </a:extLst>
       </xdr:spPr>
-    </xdr:pic>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>50265</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>600166</xdr:rowOff>
+      <xdr:colOff>99784</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>117708</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>2930122</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>592909</xdr:rowOff>
+      <xdr:colOff>2874581</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>689428</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="圖片 5"/>
+        <xdr:cNvPr id="3" name="圖片 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6342208" y="2537823"/>
-          <a:ext cx="8366257" cy="4412343"/>
+          <a:off x="5333998" y="2839137"/>
+          <a:ext cx="8244869" cy="4109577"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1" descr="data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAGMAAABjCAYAAACPO76VAAAAAXNSR0IArs4c6QAAAARnQU1BAACxjwv8YQUAAAAJcEhZcwAADsMAAA7DAcdvqGQAAAeVSURBVHhe5Y/RjhtJEgPv/3/a1zWrXcUUGBJT1XpyAAGjSWbJ87+LP3fb0Oy5oVOaW26okbY3GMMjG5o9N3RKc8sNNdL2BmN4ZEOz54ZOaW65oUba3uDz44TmHW6okba7hm2YU8M2lk/hO5f3P2pwQ4203TVsw5watrF8Ct+5vP9RgxtqpO2uYRvm1LCN5VP4zmV+lLlJmryRTHPCDSWWN9gtc5NsXTWKkiZvJNOccEOJ5Q12y9wkW1eNoqTJG8k0J9xQYnmD3TI3ydZVoyhp8qkk9a3EcnKyYW6SratGUdLkU0nqW4nl5GTD3CRbV42ipMmnktS3EsvJyYa5SbauGkVJk1PjZDPNCTcmaXKTbF01ipImp8bJZpoTbkzS5CbZumoUJU1OjZPNNCfcmKTJTbJ1eTTF3rGccHMiaXKTTPMpfOfy/keJ5YSbE0mTm2SaT+E7l/c/Siwn3JxImtwk03wK37n89XGL5G/IbzSGR5K/Ib/RGB5J/ob8Nh9vf434o5vEctJsDN5SYvm3+fqv8Q8zieWk2Ri8pcTyb/P1X+MfZhLLSbMxeEuJ5d/m+r33/6GpDeluaaTtK41m08B3phpXl0fMpzaku6WRtq80mk0D35lqXF0eMZ/akO6WRtq+0mg2DXxnqvGrSYdLwzaWN5zcGvYmc5Okfpc0+S8f/Q9xcGnYxvKGk1vD3mRuktTvkib/5aP/IQ4uDdtY3nBya9ibzE2S+l3S5JvPD+Nkw5yS1C+NtF0Sy0mzIc3eNpaTq6tGH2+YU5L6pZG2S2I5aTak2dvGcnJ11ejjDXNKUr800nZJLCfNhjR721hOfjXVQbEh3FNiOWk2U5o3uWk0qs3j3x+qg2JDuKfEctJspjRvctNoVJvHvz9UB8WGcE+J5aTZTGne5KbRKDe/H/vXKXZrudHsbcOckmk+he/Qhmv3+TGxW8uNZm8b5pRM8yl8hzZcu8+Pid1abjR72zCnZJpP4Tu04drlA+aNxHKj2XPTSJr8Lknq3/j8IMwbieVGs+emkTT5XZLUv/H5QZg3EsuNZs9NI2nyuySpf+nj7hg+akw35gnpvV2S+qVxsjn7y4D9AJluzBPSe7sk9UvjZHP2lwH7ATLdmCek93ZJ6pfGyeb6fhbUSNslSf2STHPD9k1uktQvieWk3DxH1EjbJUn9kkxzw/ZNbpLUL4nlpNw8R9RI2yVJ/ZJMc8P2TW6S1C+J5aTcfP4QczolvbGc0txyY06x2ybffH4YtmFOp6Q3llOaW27MKXbb5JvPD8M2zOmU9MZySnPLjTnFbpt8M4aPs3+Y5sQ2TU5J6pdGsyHcNxpp+8YYPp77h2lObNPklKR+aTQbwn2jkbZvjOHjuX+Y5sQ2TU5J6pdGsyHcNxpp+9LH3Q9xcGmk7a5hG+aUpH7ZkO52SeqXJPVLYjn51fCAGmm7a9iGOSWpXzaku12S+iVJ/ZJYTn41PKBG2u4atmFOSeqXDelul6R+SVK/JJaTq6tGUSNtl1PSG6+cYrffyEufHwY31Ejb5ZT0xiun2O038tLnh8ENNdJ2OSW98copdvuNvPJx90McvJBMc2Kbk5ySaT7F3rGc/Gp40EimObHNSU7JNJ9i71hOfjU8aCTTnNjmJKdkmk+xdywnV/ccNU5pbm3D3CTTnHBzopG2wRiqU5pb2zA3yTQn3JxopG0whuqU5tY2zE0yzQk3JxppG3x+NNieOT0hvbc7Jb2xPMHeYW6S6zsXhu2Z0xPSe7tT0hvLE+wd5ia5vnNh2J45PSG9tzslvbE8wd5hbpLrW4sosZxw00hSv2xo9rZpckpSv0u2rhr9J7GccNNIUr9saPa2aXJKUr9Ltq4a/SexnHDTSFK/bGj2tmlySlK/S7bu/YgwN4nlhBtKmtwkqd8lqf9EY9vlgyY3ieWEG0qa3CSp3yWp/0Rj2+WDJjeJ5YQbSprcJKnfJan/ROPX7pF9Df6YwU3jlOkt97Qh3S1J6n989F+DP2Zw0zhless9bUh3S5L6Hx/91+CPGdw0Tpneck8b0t2SpP5hDI/8Bul3lsRyws1UcldOru45ustvkH5nSSwn3Ewld+Xk6p6ju/wG6XeWxHLCzVRyV06u7v2owd5hbhLLp/AdSiwnzYbYnjkl13cuptg7zE1i+RS+Q4nlpNkQ2zOn5PrOxRR7h7lJLJ/CdyixnDQbYnvmlFzfWryVNDklqV8azcbgrUlS/4nkRf7+wCRNTknql0azMXhrktR/InmRvz8wSZNTkvql0WwM3pok9Z9IXuTvD0wyzQ3uG420XZImpw3pbklS//D5QZibZJob3DcaabskTU4b0t2SpP7h84MwN8k0N7hvNNJ2SZqcNqS7JUn9w+cHYW6SaU64uUsjbZdG2r7SKDd5xNwk05xwc5dG2i6NtH2lUW7yiLlJpjnh5i6NtF0aaftKo9y8HzVM3+G+kVhObMO80ZhuqHF170cN03e4bySWE9swbzSmG2pc3ftRw/Qd7huJ5cQ2zBuN6YYaV5cPTiSWN9gt80YjbZck9UtyY/4s7pJY3mC3zBuNtF2S1C/JjfmzuEtieYPdMm800nZJUr8k9+R//vwfkCUMHuBgm4EAAAAASUVORK5CYII="/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9959340" y="10370820"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>283028</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>293914</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6935</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>540336</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="圖片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5910942" y="1600200"/>
+          <a:ext cx="943107" cy="943107"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1001,6 +1005,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="437" row="3">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2B3F5471-674D-4F55-81C0-5D762EF97407}">
+  <we:reference id="wa104051163" version="1.2.0.3" store="zh-TW" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA104051163" version="1.2.0.3" store="WA104051163" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="工作表1">
@@ -1011,317 +1035,345 @@
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
     <col min="4" max="4" width="16.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="38.44140625" customWidth="1"/>
-    <col min="15" max="15" width="44.88671875" customWidth="1"/>
+    <col min="5" max="5" width="42.21875" customWidth="1"/>
+    <col min="15" max="15" width="48.88671875" customWidth="1"/>
     <col min="17" max="17" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-    </row>
-    <row r="3" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="21" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="25" t="str">
-        <f>"*"&amp;C3&amp;"*"</f>
+      <c r="D3" s="17" t="str">
+        <f>"*"&amp;$C$3&amp;"*"</f>
         <v>*4L12C53161*</v>
       </c>
-      <c r="E3" s="10" t="str">
-        <f t="shared" ref="E3:E11" si="0">D3</f>
+      <c r="E3" s="3" t="str">
+        <f>$D$3</f>
         <v>*4L12C53161*</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="22"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="11" t="str">
-        <f>C3</f>
+      <c r="F3" s="25"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="4" t="str">
+        <f>$C$3</f>
         <v>4L12C53161</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="21" t="s">
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="17" t="str">
+        <f>"*"&amp;$C$5&amp;"*"</f>
+        <v>*5E319*</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <f>$D$5</f>
+        <v>*5E319*</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+    </row>
+    <row r="6" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="14"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="8" t="str">
+        <f>$C$5</f>
+        <v>5E319</v>
+      </c>
+      <c r="F6" s="25"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="17" t="str">
+        <f>"*"&amp;$C$7&amp;"*"</f>
+        <v>*626206E3191*</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <f>$D$7</f>
+        <v>*626206E3191*</v>
+      </c>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="14"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="4" t="str">
+        <f>$C$7</f>
+        <v>626206E3191</v>
+      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="25" t="str">
-        <f>"*"&amp;C5&amp;"*"</f>
-        <v>*5E309*</v>
-      </c>
-      <c r="E5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>*5E309*</v>
-      </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-    </row>
-    <row r="6" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="22"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="11" t="str">
-        <f>C5</f>
-        <v>5E309</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-    </row>
-    <row r="7" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="21" t="s">
+      <c r="C9" s="15">
+        <v>375970680</v>
+      </c>
+      <c r="D9" s="17" t="str">
+        <f>"*"&amp;$C$9&amp;"*"</f>
+        <v>*375970680*</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f>$D$9</f>
+        <v>*375970680*</v>
+      </c>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="14"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="4">
+        <f>$C$9</f>
+        <v>375970680</v>
+      </c>
+      <c r="F10" s="25"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="Q10" s="6"/>
+    </row>
+    <row r="11" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="25" t="str">
-        <f t="shared" ref="D7:D11" si="1">"*"&amp;C7&amp;"*"</f>
-        <v>*625531E3091*</v>
-      </c>
-      <c r="E7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>*625531E3091*</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="22"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="11" t="str">
-        <f>C7</f>
-        <v>625531E3091</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-    </row>
-    <row r="9" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="23">
-        <v>375970680</v>
-      </c>
-      <c r="D9" s="25" t="str">
-        <f t="shared" si="1"/>
-        <v>*375970680*</v>
-      </c>
-      <c r="E9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>*375970680*</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-    </row>
-    <row r="10" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="22"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="11">
-        <f>C9</f>
-        <v>375970680</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-    </row>
-    <row r="11" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="25" t="str">
-        <f t="shared" si="1"/>
+      <c r="D11" s="17" t="str">
+        <f>"*"&amp;$C$11&amp;"*"</f>
         <v>*E1550156A*</v>
       </c>
-      <c r="E11" s="10" t="str">
-        <f t="shared" si="0"/>
+      <c r="E11" s="3" t="str">
+        <f>$D$11</f>
         <v>*E1550156A*</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="22"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="11" t="str">
-        <f>C11</f>
+      <c r="F11" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+    </row>
+    <row r="12" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="4" t="str">
+        <f>$C$11</f>
         <v>E1550156A</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
     </row>
     <row r="13" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-    </row>
-    <row r="14" spans="1:17" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+    </row>
+    <row r="14" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="4"/>
-      <c r="I14" s="18" t="s">
+      <c r="C14" s="15" t="str">
+        <f>RIGHT(C7,13)</f>
+        <v>626206E3191</v>
+      </c>
+      <c r="D14" s="17" t="str">
+        <f>"*"&amp;$C$14&amp;"*"</f>
+        <v>*626206E3191*</v>
+      </c>
+      <c r="E14" s="3" t="str">
+        <f>$D$14</f>
+        <v>*626206E3191*</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="1:17" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="14"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="4" t="str">
+        <f>$C$14</f>
+        <v>626206E3191</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="5" t="str">
+      <c r="E18" s="7" t="str">
         <f>F16&amp;C3&amp;F16&amp;C5&amp;F16&amp;C7&amp;F16&amp;C9&amp;F16&amp;C11</f>
-        <v>||4L12C53161||5E309||625531E3091||375970680||E1550156A</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E19" s="6" t="s">
+        <v>||4L12C53161||5E319||626206E3191||375970680||E1550156A</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="E19" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="L19" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="25">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="F5:O10"/>
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="F12:O12"/>
-    <mergeCell ref="F3:O9"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C13:E13"/>
@@ -1333,15 +1385,18 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="F11:O12"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B9:B10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E19" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="3.937007874015748E-2" right="0.31496062992125984" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -1351,22 +1406,19 @@
   <sheetPr codeName="工作表2"/>
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1374,10 +1426,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -1391,7 +1443,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -1402,13 +1454,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1416,13 +1468,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1430,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1444,13 +1496,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
+++ b/三合一單自動產生器/台積電槽車barcode三合一單-範本.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="barcode" sheetId="1" r:id="rId1"/>
@@ -428,11 +428,52 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -444,47 +485,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1036,36 +1036,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
@@ -1079,9 +1079,9 @@
         <f>$D$3</f>
         <v>*4L12C53161*</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1091,16 +1091,16 @@
       <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="16"/>
       <c r="D4" s="18"/>
       <c r="E4" s="4" t="str">
         <f>$C$3</f>
         <v>4L12C53161</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -1110,10 +1110,10 @@
       <c r="O4" s="5"/>
     </row>
     <row r="5" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="17" t="str">
@@ -1124,41 +1124,41 @@
         <f>$D$5</f>
         <v>*5E319*</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
     </row>
     <row r="6" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="11"/>
-      <c r="C6" s="23"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="18"/>
       <c r="E6" s="8" t="str">
         <f>$C$5</f>
         <v>5E319</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
     </row>
     <row r="7" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="17" t="str">
@@ -1169,38 +1169,38 @@
         <f>$D$7</f>
         <v>*626206E3191*</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
     </row>
     <row r="8" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11"/>
-      <c r="C8" s="25"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="18"/>
       <c r="E8" s="4" t="str">
         <f>$C$7</f>
         <v>626206E3191</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
     </row>
     <row r="9" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="15">
@@ -1214,39 +1214,39 @@
         <f>$D$9</f>
         <v>*375970680*</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
     </row>
     <row r="10" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="16"/>
       <c r="D10" s="18"/>
       <c r="E10" s="4">
         <f>$C$9</f>
         <v>375970680</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
       <c r="Q10" s="6"/>
     </row>
     <row r="11" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="15" t="s">
@@ -1260,48 +1260,48 @@
         <f>$D$11</f>
         <v>*E1550156A*</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
     </row>
     <row r="12" spans="1:17" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="16"/>
       <c r="D12" s="18"/>
       <c r="E12" s="4" t="str">
         <f>$C$11</f>
         <v>E1550156A</v>
       </c>
-      <c r="F12" s="26"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
     </row>
     <row r="13" spans="1:17" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="15" t="str">
@@ -1316,18 +1316,18 @@
         <f>$D$14</f>
         <v>*626206E3191*</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="11"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="16"/>
       <c r="D15" s="18"/>
       <c r="E15" s="4" t="str">
@@ -1358,6 +1358,15 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="25">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="F3:H4"/>
+    <mergeCell ref="F5:O10"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C13:E13"/>
@@ -1374,15 +1383,6 @@
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="F3:H4"/>
-    <mergeCell ref="F5:O10"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
